--- a/data/output/evaluasi_76.xlsx
+++ b/data/output/evaluasi_76.xlsx
@@ -11,8 +11,8 @@
     <sheet name="7601" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="7602" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="7603" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="7604" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="7605" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7605" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="7604" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="7606" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5.072421525083776</v>
+        <v>371.9934562671608</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pkp_q1-25</t>
+          <t>adhb_pi_q3-25</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -509,16 +509,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-39.32738701553591</v>
+        <v>-10.24165254517393</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25</t>
+          <t>adhb_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -533,20 +533,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-10.93407429890149</v>
+        <v>-13.0522868540302</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25</t>
+          <t>adhb_net_ekspor_q3-25</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-48.81502903582958</v>
+        <v>-15.31777617231382</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -574,7 +574,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -589,20 +589,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-12.30682588537031</v>
+        <v>7.245473215681668</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25</t>
+          <t>adhk_pi_q2-25</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi lebih dari +- 5 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -617,20 +617,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.292382253284485</v>
+        <v>-3080.752039039671</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>distribusi_pi_q1-25 vs distribusi_pi_q1-25.1</t>
+          <t>adhk_pi_q3-25</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Distribusi lebih dari +- 20 persen</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -649,16 +649,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.227484966062961</v>
+        <v>-11.84406340650931</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+          <t>adhk_net_ekspor_q1-25</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
         </is>
       </c>
     </row>
@@ -673,20 +673,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q1-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.37045756230954</v>
+        <v>-2.771369415424419</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q2-25 vs q-to-q_pklnprt_q2-25.1</t>
+          <t>q-to-q_pdrb_q1-25 vs q-to-q_pdrb_q1-25.1</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -705,16 +705,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.2851440718985171</v>
+        <v>5.320226833069812</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+          <t>q-to-q_pdrb_q2-25 vs q-to-q_pdrb_q2-25.1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth berlawanan arah</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
         </is>
       </c>
     </row>
@@ -729,20 +729,720 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1.23862204178359</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25 vs q-to-q_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>76</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D11" t="n">
-        <v>0.2126093138636469</v>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="D12" t="n">
+        <v>0.3177789414909254</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q1-25 vs q-to-q_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>76</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>25.90440583850243</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>7.475784406755591</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q2-25 vs q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>76</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5.756001952835704</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>76</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.926182962166854</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q1-25 vs y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>76</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4.008702134293656</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>76</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1.344098170119122</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>76</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>-3.236865118604071</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q1-25 vs y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>76</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>4.926182962166854</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q1-25 vs c-to-c_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>76</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>5.553102697971123</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q2-25 vs c-to-c_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>76</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>5.032673909811967</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25 vs c-to-c_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>76</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>-3.236865118604071</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q1-25 vs c-to-c_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>76</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>-0.6426804333427366</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25 vs c-to-c_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>76</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.8445549440815757</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q1-25 vs implisit_q-to-q_pkrt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>76</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>-1.953013737457481</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q1-25 vs implisit_q-to-q_pkp_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>76</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4.440836798703338</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q2-25 vs implisit_q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>76</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>-0.8943784592815038</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q3-25 vs implisit_q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>76</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>0.1698052059544568</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>implisit_q-to-q_pmtb_q1-25 vs implisit_q-to-q_pmtb_q1-25.1</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Growth berlawanan arah</t>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Nilai antara Provinsi dan total Kabupaten/Kota beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>76</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>1.089035025752752</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q2-25 vs implisit_q-to-q_pmtb_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>76</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>2.693072468512948</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25 vs implisit_q-to-q_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>76</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6.709890404133882</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q1-25 vs implisit_y-on-y_pklnprt_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>76</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>7.011088388540067</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q2-25 vs implisit_y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>76</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>5.255565934926706</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>76</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4.441237417374686</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25 vs implisit_y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>76</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sulawesi Barat</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>q1-25</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6.836750735235634</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q1-25 vs implisit_y-on-y_pmtb_q1-25.1</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -757,7 +1457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -807,7 +1507,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-26948.49489857</v>
+        <v>-56427.64</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -816,7 +1516,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -835,7 +1535,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>24116.00048662676</v>
+        <v>33105</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -844,7 +1544,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -863,7 +1563,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-23476.5018024779</v>
+        <v>-19746.8275239581</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -872,7 +1572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -887,20 +1587,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>57386.97499999998</v>
+        <v>4804.37482472159</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -915,20 +1615,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.1486578578282809</v>
+        <v>-1770.177524769446</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>q-to-q_pklnprt_q1-25_ril vs q-to-q_pklnprt_q1-25_rev</t>
+          <t>adhk_net_ekspor_q2-25_ril vs adhk_net_ekspor_q2-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -947,16 +1647,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.5557195639575788</v>
+        <v>0.3971626181571108</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -971,20 +1671,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.85314082040881</v>
+        <v>0.9449883112091609</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1003,16 +1703,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.5557195639575788</v>
+        <v>8.481488945184685</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1031,16 +1731,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2.85314082040881</v>
+        <v>-0.08927206255489142</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -1055,20 +1755,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.5637768311618196</v>
+        <v>2.421654362465933</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkrt_q1-25_ril vs implisit_q-to-q_pkrt_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -1083,20 +1783,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.693846784711576</v>
+        <v>0.1030517139400783</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1111,20 +1811,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-3.587787635001728</v>
+        <v>0.3507875295290933</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1139,188 +1839,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-4.337223064569817</v>
+        <v>3.115648460758464</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>3.365874173716062</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>0.001703791193008905</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>sog_q_pklnprt_q1-25_ril vs sog_q_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>-0.4386133025853751</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>0.007003249935001218</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3837236445941002</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>7601</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Kabupaten Majene</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>-1.417709611819135</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1385,7 +1917,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>62548.4807215797</v>
+        <v>52789.27316957509</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1394,7 +1926,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1409,20 +1941,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26271.2419436592</v>
+        <v>114574.9101433746</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>adhb_pi_q2-25_ril vs adhb_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1441,16 +1973,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.31016877997205</v>
+        <v>21670.57895750081</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1465,20 +1997,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01406926822832391</v>
+        <v>7.235685975298354</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>q-to-q_pmtb_q2-25_ril vs q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1493,20 +2025,104 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.022765305827538</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D6" t="n">
-        <v>5.966747936186172</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>implisit_y-on-y_pklnprt_q1-25_ril vs implisit_y-on-y_pklnprt_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+      <c r="D7" t="n">
+        <v>-2.524978213594188</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0.183969271359212</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7602</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Polewali Mandar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3.168097225665498</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1521,7 +2137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1571,7 +2187,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-14623.3097311984</v>
+        <v>-8159.31540339673</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1580,7 +2196,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1599,7 +2215,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-302.423494157847</v>
+        <v>-6439.411442096</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1608,7 +2224,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1623,20 +2239,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.1980590671742999</v>
+        <v>2101.66343746311</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pklnprt_q1-25_ril vs y-on-y_pklnprt_q1-25_rev</t>
+          <t>adhk_pi_q2-25_ril vs adhk_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
@@ -1651,20 +2267,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.427722126331066</v>
+        <v>-1.282780697989502</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pkp_q1-25_ril vs y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -1683,16 +2299,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-6.537390864496839</v>
+        <v>-0.1058680604481227</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
@@ -1707,20 +2323,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.1980590671742999</v>
+        <v>3.170234614318294</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>c-to-c_pklnprt_q1-25_ril vs c-to-c_pklnprt_q1-25_rev</t>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1735,20 +2351,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>6.427722126331066</v>
+        <v>-0.1874523179208729</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q1-25_ril vs c-to-c_pkp_q1-25_rev</t>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1763,20 +2379,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-6.537390864496839</v>
+        <v>0.4831265025665581</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1791,20 +2407,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.03798038414697281</v>
+        <v>-0.5775434776320785</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pklnprt_q1-25_ril vs implisit_q-to-q_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pklnprt_q3-25_prov vs implisit_q-to-q_pklnprt_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1819,20 +2435,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1.41670093182403</v>
+        <v>2.651213061107379</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>implisit_q-to-q_pkp_q3-25_prov vs implisit_q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1847,20 +2463,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.003800238914917189</v>
+        <v>2.885737598863984</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pklnprt_q1-25_ril vs sog_y-on-y_pklnprt_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1875,76 +2491,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1.023431661123349</v>
+        <v>3.319247897467608</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pkp_q1-25_ril vs sog_y-on-y_pkp_q1-25_rev</t>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>7603</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Kabupaten Mamasa</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>-1.72678916202618</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>7603</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Kabupaten Mamasa</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>q1-25</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>0.9394346989880088</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1959,7 +2519,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1996,11 +2556,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7604</v>
+        <v>7605</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Mamuju</t>
+          <t>Kabupaten Pasangkayu</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2009,7 +2569,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-5155.675556085631</v>
+        <v>-12539.506148577</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2018,17 +2578,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7604</v>
+        <v>7605</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Mamuju</t>
+          <t>Kabupaten Pasangkayu</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2037,26 +2597,26 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>296777.9138944163</v>
+        <v>-15707.001404793</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhb_net_ekspor_q1-25_ril vs adhb_net_ekspor_q1-25_rev</t>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7604</v>
+        <v>7605</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Mamuju</t>
+          <t>Kabupaten Pasangkayu</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2065,44 +2625,240 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-3441.2126415227</v>
+        <v>2.958838972248919</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7604</v>
+        <v>7605</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Mamuju</t>
+          <t>Kabupaten Pasangkayu</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.247744944880394</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>q1-25</t>
         </is>
       </c>
-      <c r="D5" t="n">
-        <v>158507.071627897</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+      <c r="D6" t="n">
+        <v>-7.075100965684654</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.769046043247851</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.8326495127909</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>9.961730519483014</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pdrb_q3-25_prov vs c-to-c_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1070215030026755</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-5.750944638728425</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7605</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Pasangkayu</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-5.988247596504574</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>sog_y-on-y_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2154,11 +2910,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -2167,54 +2923,54 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-64077.961812468</v>
+        <v>-3441.2126415227</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi lebih dari (+-30%) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-40577.8839943823</v>
+        <v>0.2327261074133373</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>c-to-c_pmtb_q2-25_ril vs c-to-c_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -2223,54 +2979,54 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-1.183154224709815</v>
+        <v>3.116986727011529</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.183154224709815</v>
+        <v>0.2883231422697057</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>implisit_q-to-q_pmtb_q2-25_ril vs implisit_q-to-q_pmtb_q2-25_rev</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2279,26 +3035,26 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-3.056294710226975</v>
+        <v>9.302126386645552</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pmtb_q1-25_ril vs implisit_q-to-q_pmtb_q1-25_rev</t>
+          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2307,54 +3063,54 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.109091987237464</v>
+        <v>-2.535586550193871</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pkp_q1-25_ril vs implisit_y-on-y_pkp_q1-25_rev</t>
+          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.461548586847084</v>
+        <v>3.200127636627827</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>implisit_y-on-y_pmtb_q1-25_ril vs implisit_y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2363,44 +3119,240 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.738191926240281</v>
+        <v>-3.901162922305095</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>sog_q_pi_q1-25_ril vs sog_q_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Growth revisi berlawanan arah</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>7605</v>
+        <v>7604</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kabupaten Pasangkayu</t>
+          <t>Kabupaten Mamuju</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.3794335881426644</v>
+        <v>-0.4293184118684441</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.19664332544642</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.50201300279804</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q3-25_prov vs c-to-c_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>0.2731789119837185</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q3-25_prov vs implisit_q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1.51272262033302</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.623996240147359</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3.04655798363948</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>7604</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-3.031847357293259</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2415,7 +3367,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2461,20 +3413,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-821.9520944369609</v>
+        <v>8.651495933101362</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhb_pi_q1-25_ril vs adhb_pi_q1-25_rev</t>
+          <t>sog_q_pi_q2-25_ril vs sog_q_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2493,16 +3445,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-513.3683269446201</v>
+        <v>-4.39484648279535</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>adhk_pi_q1-25_ril vs adhk_pi_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q1-25_ril vs sog_y-on-y_pi_q1-25_rev</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2517,20 +3469,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q2-25</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14200.92142441301</v>
+        <v>2.122065220446554</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>sog_y-on-y_pi_q2-25_ril vs sog_y-on-y_pi_q2-25_rev</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>
@@ -2545,20 +3497,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-1.693273787613787</v>
+        <v>-0.4042731495931931</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>y-on-y_pmtb_q1-25_ril vs y-on-y_pmtb_q1-25_rev</t>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2573,20 +3525,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.693273787613787</v>
+        <v>15.92640523977053</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>c-to-c_pmtb_q1-25_ril vs c-to-c_pmtb_q1-25_rev</t>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2601,20 +3553,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2.590832102688342</v>
+        <v>8.6832162967006</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>implisit_q-to-q_pkp_q1-25_ril vs implisit_q-to-q_pkp_q1-25_rev</t>
+          <t>q-to-q_pmtb_q3-25_prov vs q-to-q_pmtb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2629,20 +3581,244 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.4150923689232013</v>
+        <v>1.360993347547697</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>sog_y-on-y_pmtb_q1-25_ril vs sog_y-on-y_pmtb_q1-25_rev</t>
+          <t>y-on-y_pdrb_q3-25_prov vs y-on-y_pdrb_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Growth revisi lebih dari +- 50 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.5555787809144619</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25_prov vs y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.3949387788722921</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25_prov vs y-on-y_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.751441511690777</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q3-25_prov vs c-to-c_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-1.089231952088043</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkrt_q3-25_prov vs implisit_q-to-q_pkrt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.6748415868297033</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q3-25_prov vs implisit_q-to-q_pmtb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>9.463673751630713</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_q3-25_prov vs implisit_y-on-y_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.63284420566781</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pklnprt_q3-25_prov vs implisit_y-on-y_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7606</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Mamuju Tengah</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.8756366192391</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q3-25</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_76.xlsx
+++ b/data/output/evaluasi_76.xlsx
@@ -686,7 +686,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,3 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -826,7 +826,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -882,7 +882,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -910,7 +910,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -938,7 +938,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1050,7 +1050,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
